--- a/artfynd/A 55214-2024 artfynd.xlsx
+++ b/artfynd/A 55214-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031800</v>
       </c>
       <c r="B2" t="n">
-        <v>78365</v>
+        <v>78367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55214-2024 artfynd.xlsx
+++ b/artfynd/A 55214-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031800</v>
       </c>
       <c r="B2" t="n">
-        <v>78367</v>
+        <v>78368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55214-2024 artfynd.xlsx
+++ b/artfynd/A 55214-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031800</v>
       </c>
       <c r="B2" t="n">
-        <v>78368</v>
+        <v>78375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55214-2024 artfynd.xlsx
+++ b/artfynd/A 55214-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031800</v>
       </c>
       <c r="B2" t="n">
-        <v>78381</v>
+        <v>78382</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55214-2024 artfynd.xlsx
+++ b/artfynd/A 55214-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031800</v>
       </c>
       <c r="B2" t="n">
-        <v>78382</v>
+        <v>78387</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
